--- a/artfynd/A 47407-2020 artfynd.xlsx
+++ b/artfynd/A 47407-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47407-2020 artfynd.xlsx
+++ b/artfynd/A 47407-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2024,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>94212487</v>
+        <v>116163105</v>
       </c>
       <c r="B14" t="n">
-        <v>89410</v>
+        <v>90433</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,20 +2057,31 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stora Syltvik, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>602036.6153202703</v>
+        <v>602037</v>
       </c>
       <c r="R14" t="n">
-        <v>6445588.400151526</v>
+        <v>6445588</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2094,22 +2105,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-06-12</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-06-12</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-22</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Återfynd. Ungefärligt antal fruktkroppar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2118,18 +2124,34 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>David Ek</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>David Ek, Nina Marliden, Marika Sjödin</t>
+          <t>Stefan Kasselstrand, Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -6654,140 +6676,6 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>116163105</v>
-      </c>
-      <c r="B55" t="n">
-        <v>90433</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Stora Syltvik, Ög</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>602037</v>
-      </c>
-      <c r="R55" t="n">
-        <v>6445588</v>
-      </c>
-      <c r="S55" t="n">
-        <v>5</v>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Valdemarsvik</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Gryt</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2024-04-22</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>2024-04-22</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Återfynd. Ungefärligt antal fruktkroppar.</t>
-        </is>
-      </c>
-      <c r="AD55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF55" t="inlineStr"/>
-      <c r="AG55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr">
-        <is>
-          <t>Stefan Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>Stefan Kasselstrand, Mats Oldenborg</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
